--- a/etf_holdings/2026-10-27_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-27_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,55 +1184,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-4,000,000</t>
-        </is>
-      </c>
+        <v>480000</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>2026-10-26_00403A_full_holdings.xlsx</t>
@@ -1247,55 +1229,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
+          <t>長興</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.12%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2,000,000</t>
-        </is>
-      </c>
+        <v>900000</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>2026-10-26_00403A_full_holdings.xlsx</t>
@@ -1310,55 +1274,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
+          <t>上銀</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.65%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>5.77%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>+0.12%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2275000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2330000</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>55,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>2026-10-26_00403A_full_holdings.xlsx</t>
@@ -1373,55 +1319,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K16" t="n">
-        <v>400000</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>399,000</t>
-        </is>
-      </c>
+        <v>90000</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>2026-10-26_00403A_full_holdings.xlsx</t>
@@ -1436,55 +1364,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.98%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2.16%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>+0.18%</t>
-        </is>
-      </c>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>156500</v>
-      </c>
-      <c r="K17" t="n">
-        <v>170500</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>14,000</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>2026-10-26_00403A_full_holdings.xlsx</t>
@@ -1494,507 +1404,367 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1.89%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-2.16%</t>
-        </is>
-      </c>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>278000</v>
-      </c>
-      <c r="K18" t="n">
-        <v>128000</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-150,000</t>
-        </is>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-26_00405A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.07%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2.56%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-3.51%</t>
-        </is>
-      </c>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>173000</v>
-      </c>
-      <c r="K19" t="n">
-        <v>73000</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
+        <v>2000000</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-26_00405A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>達發</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>達發</t>
-        </is>
-      </c>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.53%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>146000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-145,000</t>
-        </is>
-      </c>
+        <v>3200000</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-26_00405A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>富世達</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>富世達</t>
-        </is>
-      </c>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.69%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2.87%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-0.82%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>341000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>271000</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-70,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-26_00405A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.06%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>+0.55%</t>
-        </is>
-      </c>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>1395000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1795000</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>400,000</t>
-        </is>
-      </c>
+        <v>1600000</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-26_00407A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1.87%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>+0.55%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>113000</v>
-      </c>
-      <c r="K23" t="n">
-        <v>153000</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-26_00407A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
-        </is>
-      </c>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>54000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>104000</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
+        <v>820000</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-26_00407A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.71%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1.94%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-0.77%</t>
-        </is>
-      </c>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>389000</v>
-      </c>
-      <c r="K25" t="n">
-        <v>309000</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>-80,000</t>
-        </is>
-      </c>
+        <v>2800000</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-26_00407A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2009,37 +1779,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>200000</v>
+        <v>4000000</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,37 +1824,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>70000</v>
+        <v>200000</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2099,37 +1869,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>4192000</v>
+        <v>350000</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2144,37 +1914,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>1107336</v>
+        <v>4000000</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2189,37 +1959,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>960000</v>
+        <v>2000000</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2234,37 +2004,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>708000</v>
+        <v>375000</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2279,37 +2049,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>252000</v>
+        <v>2000000</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2324,37 +2094,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>999000</v>
+        <v>1000</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2369,37 +2139,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>1871000</v>
+        <v>1500000</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2414,37 +2184,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1424000</v>
+        <v>800000</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2459,37 +2229,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>3104000</v>
+        <v>1460000</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2504,37 +2274,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>6547000</v>
+        <v>1000</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2549,37 +2319,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>76000</v>
+        <v>156500</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2594,37 +2364,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>2208000</v>
+        <v>1000</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2639,37 +2409,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>1287000</v>
+        <v>1000</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2684,37 +2454,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>82000</v>
+        <v>350000</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2729,37 +2499,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>592000</v>
+        <v>350000</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2774,37 +2544,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>大量</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>115000</v>
+        <v>300000</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2819,37 +2589,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>1614000</v>
+        <v>310000</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2864,37 +2634,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>133000</v>
+        <v>1000</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2909,37 +2679,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>245000</v>
+        <v>1000</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2954,750 +2724,593 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>142000</v>
+        <v>1880000</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>嘉澤</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.91%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+          <t>5.65%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>5.77%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
       <c r="J48" t="n">
-        <v>152000</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+        <v>2275000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2330000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-2.16%</t>
+        </is>
+      </c>
       <c r="J49" t="n">
-        <v>184000</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+        <v>278000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>128000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-150,000</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-3.51%</t>
+        </is>
+      </c>
       <c r="J50" t="n">
-        <v>228000</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+        <v>173000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>73000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>達發</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>達發</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.01%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>464000</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+        <v>146000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-145,000</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2.87%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-0.82%</t>
+        </is>
+      </c>
       <c r="J52" t="n">
-        <v>257000</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+        <v>341000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>271000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-70,000</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.52%</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>2.06%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+0.55%</t>
+        </is>
+      </c>
       <c r="J53" t="n">
-        <v>28400</v>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+        <v>1395000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1795000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>400,000</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>崇越</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+0.55%</t>
+        </is>
+      </c>
       <c r="J54" t="n">
-        <v>200000</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+        <v>113000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>153000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>新普</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.22%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
       <c r="J55" t="n">
-        <v>178000</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+        <v>54000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>104000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.88%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
       <c r="J56" t="n">
-        <v>1293000</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+        <v>389000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>309000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-80,000</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1.05%</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>249000</v>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>6271</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>同欣電</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>340000</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>279000</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1.54%</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
-        <v>4327000</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>7750</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>新代</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>0.74%</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>122000</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0.70%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>40000</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>宏全</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>180000</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-10-26_00400A_full_holdings.xlsx</t>
+          <t>2026-10-26_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
